--- a/勤怠/勤怠_テスト太郎.xlsx
+++ b/勤怠/勤怠_テスト太郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5DEDCD-98F9-4E70-A509-7F6A2A376CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E149AA7-B963-443C-BF36-C1519CF83C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7410" yWindow="7410" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -439,11 +439,11 @@
         <v>0.375</v>
       </c>
       <c r="F6" s="1">
-        <v>0.91666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" ref="G6:G35" si="0">F6-E6</f>
-        <v>0.54166666666666663</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -514,11 +514,11 @@
         <v>0.375</v>
       </c>
       <c r="F11" s="1">
-        <v>20</v>
+        <v>0.75</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>19.625</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -604,11 +604,11 @@
         <v>0.375</v>
       </c>
       <c r="F17" s="1">
-        <v>0.91666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="0"/>
-        <v>0.54166666666666663</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -694,11 +694,11 @@
         <v>0.375</v>
       </c>
       <c r="F23" s="1">
-        <v>0.75</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="0"/>
-        <v>0.375</v>
+        <v>0.54166666666666663</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -709,11 +709,11 @@
         <v>0.375</v>
       </c>
       <c r="F24" s="1">
-        <v>0.91666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="0"/>
-        <v>0.54166666666666663</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="25" spans="1:7">

--- a/勤怠/勤怠_テスト太郎.xlsx
+++ b/勤怠/勤怠_テスト太郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E149AA7-B963-443C-BF36-C1519CF83C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406B7C12-52CA-4246-97B2-5034F972FDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7410" yWindow="7410" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6630" yWindow="6630" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
